--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,6 +1152,130 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125634824</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98175</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>504</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östra höjden II, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>463334</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6639175</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>"Ny" lokal. Delgiven av Anders Tedeholm efter tips från lokalbefolkning. 4 knoppar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Teodorsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Teodorsson, Pär Dahlström, Gunnar Flygh, anders tedeholm, Jan-Anders Aronson, Arne Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,12 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Teodorsson, Pär Dahlström, Gunnar Flygh, anders tedeholm, Jan-Anders Aronson, Arne Berglund</t>
+          <t>Arne Berglund, Jan-Anders Aronson, anders tedeholm, Gunnar Flygh, Pär Dahlström, Jan Teodorsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Arne Berglund, Jan-Anders Aronson, anders tedeholm, Gunnar Flygh, Pär Dahlström, Jan Teodorsson</t>
+          <t>Jan Teodorsson, Pär Dahlström, Gunnar Flygh, anders tedeholm, Jan-Anders Aronson, Arne Berglund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 30023-2020 artfynd.xlsx
+++ b/artfynd/A 30023-2020 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>125634824</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
